--- a/healthcare_forms/049_covid_19_mandatory_daily_health_screening_questionnaire--healthcare_forms.xlsx
+++ b/healthcare_forms/049_covid_19_mandatory_daily_health_screening_questionnaire--healthcare_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -868,7 +868,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C26"/>
+  <dimension ref="A1:C23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
@@ -1020,12 +1020,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>sore_throat</t>
+          <t>diarrhea</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Sore Throat</t>
+          <t>Diarrhea</t>
         </is>
       </c>
     </row>
@@ -1037,12 +1037,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>diarrhea</t>
+          <t>nausea</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Diarrhea</t>
+          <t>Nausea</t>
         </is>
       </c>
     </row>
@@ -1054,12 +1054,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>nausea</t>
+          <t>vomiting</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Nausea</t>
+          <t>Vomiting</t>
         </is>
       </c>
     </row>
@@ -1071,12 +1071,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>vomiting</t>
+          <t>confusion</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Vomiting</t>
+          <t>Confusion</t>
         </is>
       </c>
     </row>
@@ -1088,12 +1088,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>confusion</t>
+          <t>fatigue</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Confusion</t>
+          <t>Fatigue</t>
         </is>
       </c>
     </row>
@@ -1105,12 +1105,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>headache</t>
+          <t>runny_eyes</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Headache</t>
+          <t>Runny eyes</t>
         </is>
       </c>
     </row>
@@ -1122,12 +1122,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>fatigue</t>
+          <t>coughing_up_blood</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Fatigue</t>
+          <t>Coughing up blood</t>
         </is>
       </c>
     </row>
@@ -1139,12 +1139,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>runny_eyes</t>
+          <t>chest_pain</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Runny eyes</t>
+          <t>Chest pain</t>
         </is>
       </c>
     </row>
@@ -1156,163 +1156,112 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>coughing_up_blood</t>
+          <t>difficulty_breathing</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Coughing up blood</t>
+          <t>Difficulty breathing</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>symptoms_yes_choices</t>
+          <t>travel_history_choices</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>chest_pain</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Chest pain</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>symptoms_yes_choices</t>
+          <t>travel_history_choices</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>shortness_of_breath</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Shortness of breath</t>
+          <t>False</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>symptoms_yes_choices</t>
+          <t>contact_history_choices</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>difficulty_breathing</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Difficulty breathing</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>travel_history_choices</t>
+          <t>contact_history_choices</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>true</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>travel_history_choices</t>
+          <t>symptoms_2_choices</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>false</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>contact_history_choices</t>
+          <t>symptoms_2_choices</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>true</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>contact_history_choices</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>symptoms_2_choices</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>true</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>symptoms_2_choices</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
         <is>
           <t>False</t>
         </is>
